--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_18-07-2025.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
